--- a/results/Int All Data 0.4/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.4/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0002365268530667642</v>
+        <v>-0.0001694072806583413</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.000408783904492881</v>
+        <v>0.0004581683537078773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001373312293294992</v>
+        <v>0.0005224279397247498</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0005451762227780511</v>
+        <v>0.0002023927410392612</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001241281705530839</v>
+        <v>0.0003318290330079443</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.536028627573293e-05</v>
+        <v>0.0003917350552859567</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001477603549807316</v>
+        <v>0.0007124634961605248</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0009043834773578253</v>
+        <v>-0.0007376734655545692</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0009372124561248186</v>
+        <v>-0.0007538385173358153</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001634184247331771</v>
+        <v>-7.554937406051287e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002625113810123725</v>
+        <v>-0.000179576095076327</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0002997658010520654</v>
+        <v>0.0001003507028359529</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003401371807341825</v>
+        <v>-0.0004139449115786909</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005879213811914297</v>
+        <v>0.0006247322855785697</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0002302138895420102</v>
+        <v>-0.0007784007527783688</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002151705902204638</v>
+        <v>0.0006908748567351141</v>
       </c>
       <c r="R3" t="n">
-        <v>5.905509519344874e-05</v>
+        <v>0.0001732868857221337</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001328764932512918</v>
+        <v>0.0001458238571249847</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0003479453263225807</v>
+        <v>-0.0001421742761486888</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0009275834135091199</v>
+        <v>-1.024711823410238e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0002963640068333262</v>
+        <v>0.0004327216610066707</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000424208238718784</v>
+        <v>0.0002924455691958437</v>
       </c>
       <c r="X3" t="n">
-        <v>9.756413927489724e-05</v>
+        <v>-0.0005737914179942782</v>
       </c>
       <c r="Y3" t="n">
-        <v>-5.58003684961894e-05</v>
+        <v>-7.444786055959221e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.901630767558677e-05</v>
+        <v>0.001101920105162876</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000504523941752142</v>
+        <v>-0.001031486089805368</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0001268164173197961</v>
+        <v>-3.106213380100197e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.001798248619701567</v>
+        <v>0.001416317205497675</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00284442481136139</v>
+        <v>0.003280803592239314</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.003646861007955188</v>
+        <v>0.001595763823186367</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001118469097616188</v>
+        <v>-0.0003228621874198612</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.000879140851358</v>
+        <v>-0.0001198248793724</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0002121093721971945</v>
+        <v>0.0001503567167248677</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.00132546557911756</v>
+        <v>0.0009508487404453127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.003868491504947056</v>
+        <v>1.980878763349182e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.005163670242223639</v>
+        <v>0.00716147611439963</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0007916368719896406</v>
+        <v>0.0004380251587306649</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002979333873953949</v>
+        <v>0.0007923363938544603</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0009931355282653742</v>
+        <v>0.000167908352525884</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0009117095616885051</v>
+        <v>-0.002149078804535309</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0005027926873236888</v>
+        <v>-0.0006719853014234689</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0007653994030683498</v>
+        <v>-0.0005831279975324087</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.002822203979313999</v>
+        <v>-0.0008004796566947137</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0004321227339419665</v>
+        <v>-7.510385009131039e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0003599685806713016</v>
+        <v>-0.001713173784213758</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0002552818510243394</v>
+        <v>-2.408155230616549e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.179395080699535e-05</v>
+        <v>-0.0002639033593166473</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0001780109623897896</v>
+        <v>-0.0005745596732055758</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001601729567284971</v>
+        <v>-0.0005193574827627101</v>
       </c>
       <c r="AY3" t="n">
-        <v>-5.133862400709121e-05</v>
+        <v>0.0001142800026192836</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00180153565959138</v>
+        <v>0.001037798356576582</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0007891183212272214</v>
+        <v>-0.001529840300076205</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0004089937802350929</v>
+        <v>0.001823694248056209</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.000165378522256352</v>
+        <v>-2.333095923496065e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0001215592621753092</v>
+        <v>-0.0003526932773169866</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.00107521377184225</v>
+        <v>-0.001570087714642539</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0001655916968159254</v>
+        <v>0.0002289351584217942</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0004675432226413811</v>
+        <v>-0.0001571602214872399</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.000662666034093109</v>
+        <v>-0.0002449904798100389</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0003031479275421198</v>
+        <v>0.001670653475172556</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003520531049150953</v>
+        <v>0.0002332764243769048</v>
       </c>
       <c r="BK3" t="n">
-        <v>-5.767207802493506e-05</v>
+        <v>-0.0001515111567987758</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002271281829875515</v>
+        <v>-0.0001434510770502961</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0006950786860486456</v>
+        <v>0.0004489131661071122</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0004973518366748785</v>
+        <v>-0.001230408462009603</v>
       </c>
       <c r="BO3" t="n">
-        <v>-4.765691816695284e-05</v>
+        <v>-8.475384030955154e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0008637366708475092</v>
+        <v>-0.0007502759107510293</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0009540199856969088</v>
+        <v>-0.0006421335853847422</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0008910537480177182</v>
+        <v>0.0007463691317460329</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0007685913948921652</v>
+        <v>-0.0002103088675799325</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.000190941510162208</v>
+        <v>-0.0009716818345796574</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001125108248037058</v>
+        <v>-0.0009456989719946942</v>
       </c>
       <c r="BW3" t="n">
-        <v>-7.213246880161673e-05</v>
+        <v>1.694160481621631e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>6.007200785955622e-05</v>
+        <v>0.0002815273249371607</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.002123924076262086</v>
+        <v>0.0006798904778382642</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0007542785351304249</v>
+        <v>0.001111455454988669</v>
       </c>
       <c r="CA3" t="n">
-        <v>-4.482133418111322e-05</v>
+        <v>0.000171411750883208</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0001257817910469749</v>
+        <v>-7.761732423562263e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.000212418372289701</v>
+        <v>-0.0006483008613559072</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0001976378723066874</v>
+        <v>0.0005720913231080371</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0003353563574711871</v>
+        <v>0.0001348556656923793</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003592857277058414</v>
+        <v>-0.001031579045948889</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0001858418242799131</v>
+        <v>-0.00110794093543444</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0005818940032524234</v>
+        <v>0.0001860978120937629</v>
       </c>
       <c r="CI3" t="n">
-        <v>-1.359520690068284e-05</v>
+        <v>-0.000758216721128635</v>
       </c>
       <c r="CJ3" t="n">
-        <v>4.632562537670748e-05</v>
+        <v>4.496089035271877e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0006878893696868794</v>
+        <v>0.0001035801610211551</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.001142181250674515</v>
+        <v>0.0002071226736963692</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.0003476699384868232</v>
+        <v>4.212586458394064e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0001401709796102968</v>
+        <v>0.0001028104497842408</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0001437385246257727</v>
+        <v>-0.0008200628533568144</v>
       </c>
       <c r="CP3" t="n">
-        <v>3.81089365248588e-05</v>
+        <v>0.0001346540976615829</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0006506577983718786</v>
+        <v>0.0004391898664347071</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0006499628955439318</v>
+        <v>-0.001684714228325168</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0002782370213995378</v>
+        <v>-0.0004140997041545081</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0005947803580639255</v>
+        <v>0.0003692069819165278</v>
       </c>
       <c r="CU3" t="n">
-        <v>3.854850453667292e-06</v>
+        <v>-0.0001086178936429805</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.550608667259204e-05</v>
+        <v>-1.682716957097319e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-3.49873062302831e-06</v>
+        <v>-0.001270552152839129</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.0002498467754624001</v>
+        <v>0.001308468313375005</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-3.54621254951537e-05</v>
+        <v>8.343932728527292e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>3.023253806516024e-05</v>
+        <v>-0.000280647191264124</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0008555428254902898</v>
+        <v>9.598664532240231e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0006164183025234792</v>
+        <v>-0.0006123982825944264</v>
       </c>
       <c r="DD3" t="n">
-        <v>9.415071078009317e-05</v>
+        <v>-4.162769732299904e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.0002615710294021101</v>
+        <v>0.0002502996976820082</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0006153323406522171</v>
+        <v>-0.001773878853520589</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.278862794602211e-05</v>
+        <v>-0.0002952735374953608</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0001984132113192339</v>
+        <v>-0.0005320665064574681</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.000260659069005389</v>
+        <v>-0.0002437211432497466</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0002203875281017586</v>
+        <v>-2.900499088716031e-06</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0002460896151911951</v>
+        <v>0.0001008417200097755</v>
       </c>
       <c r="DL3" t="n">
-        <v>7.50490064051601e-05</v>
+        <v>1.600004896215035e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-1.108559414334297e-05</v>
+        <v>0.0001730502648353504</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0002846347708013098</v>
+        <v>-0.001190221486028573</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001382914078781721</v>
+        <v>-0.001553429361757608</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0004973242065758432</v>
+        <v>-0.001012033555709213</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.0001406369218786518</v>
+        <v>-0.0001015691505627248</v>
       </c>
       <c r="DR3" t="n">
-        <v>-4.718519734321247e-05</v>
+        <v>0.00017237712588418</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.0008831519394453969</v>
+        <v>-9.005642375981338e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0001128995059892857</v>
+        <v>-0.0004559378793590619</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0005521059525466809</v>
+        <v>-0.0001771413894832131</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-1.527118803456684e-05</v>
+        <v>-0.0001648196623321729</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.000390633586170438</v>
+        <v>-0.0003749740832892145</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0011944134216859</v>
+        <v>0.0004006363717042638</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001294527578100002</v>
+        <v>-4.073282788805255e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0003408160778764801</v>
+        <v>0.0002052892306221888</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0001616956701588091</v>
+        <v>0.0001845282973198925</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.000215162379088879</v>
+        <v>0.0001737622767049252</v>
       </c>
       <c r="ED3" t="n">
-        <v>7.609362173768277e-06</v>
+        <v>0.0006441768796540359</v>
       </c>
       <c r="EE3" t="n">
-        <v>-6.887054073799969e-05</v>
+        <v>1.290877796901957e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>9.090361642157042e-05</v>
+        <v>-0.0007077991876032741</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.000211337808383274</v>
+        <v>-0.0004648906851058931</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0001649382365017449</v>
+        <v>0.0001034074607312097</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0003752825602558841</v>
+        <v>-0.0002257467814508651</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0003861744805706569</v>
+        <v>-8.056869545616904e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0005709042190806435</v>
+        <v>0.0003502037512616629</v>
       </c>
       <c r="EL3" t="n">
-        <v>8.514261387824185e-06</v>
+        <v>-7.932804479701349e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.002952406560564e-05</v>
+        <v>0.0001353190527805259</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0002708584600534059</v>
+        <v>2.230750296787876e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>5.682987114586813e-05</v>
+        <v>6.790989384441781e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0004504467856851835</v>
+        <v>4.758398185864656e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-3.733084461035929e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-5.021555043250858e-06</v>
+        <v>6.338196752593949e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0001187690077223058</v>
+        <v>0.0001526581509184855</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0001731892050391681</v>
+        <v>-4.828646276330297e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>-8.784799884916655e-06</v>
+        <v>-3.82588108174442e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0003510629387595787</v>
+        <v>0.0002414211806573141</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0005078653127687349</v>
+        <v>0.0004812951308434377</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0001287976463540463</v>
+        <v>0.0001065710831556277</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003063212907042593</v>
+        <v>0.003470799471854246</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001371080591794879</v>
+        <v>0.0007508809211734459</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009302699176609328</v>
+        <v>0.001401901937887285</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001804207098787327</v>
+        <v>0.00120368907704654</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006873894239950619</v>
+        <v>0.0006231732571779177</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001590903661915409</v>
+        <v>0.002389212583300755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001193292832513472</v>
+        <v>0.003751461694054722</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001552703062967952</v>
+        <v>0.002841137970204705</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001615464350680355</v>
+        <v>0.002026773038802245</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001014589559730208</v>
+        <v>0.0008550738589865527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004483242904862296</v>
+        <v>0.0003729483270569301</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008778626073967614</v>
+        <v>0.001486550707959918</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002214229412206264</v>
+        <v>0.002842445364617231</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001203641766612952</v>
+        <v>0.002621886759120161</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009807905754773457</v>
+        <v>0.001649856328292239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004552074982546222</v>
+        <v>0.005730544511406284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001115364082209993</v>
+        <v>0.001998610769738585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002624215494813351</v>
+        <v>0.005948265779269609</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005190179104603448</v>
+        <v>0.0008538685212169074</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001809090439021577</v>
+        <v>0.00127924096533424</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001351670491136349</v>
+        <v>0.002800283524477415</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007617829288541058</v>
+        <v>0.00336289985086447</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002787365948732364</v>
+        <v>0.003491037002845591</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002415936396968624</v>
+        <v>0.001095638770751852</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001841168112363083</v>
+        <v>0.002102882620405516</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001980962023071353</v>
+        <v>0.008306212214335225</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004286540006930404</v>
+        <v>0.0003319709174000138</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.00374069127026727</v>
+        <v>0.003004928815030476</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004474516096180828</v>
+        <v>0.00428397410711309</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.009795070207805947</v>
+        <v>0.008770649618030623</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003736140775382705</v>
+        <v>0.003497885057596321</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001263649872255056</v>
+        <v>0.001374002562142929</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001022291974998682</v>
+        <v>0.00166145051430605</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002037237013318619</v>
+        <v>0.001753301938421924</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005941927960949863</v>
+        <v>0.003693520553305743</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01758969932063628</v>
+        <v>0.01346518705267993</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.000993473546931435</v>
+        <v>0.001137097100458255</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005252255854918475</v>
+        <v>0.007335649152622514</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002047946783876638</v>
+        <v>0.002819064865686718</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00250780247913159</v>
+        <v>0.002972443800677984</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0005670038586521937</v>
+        <v>0.00234417308239067</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002256790109436731</v>
+        <v>0.002804198958270218</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.009241253603305112</v>
+        <v>0.008056519727332593</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.000971628712523533</v>
+        <v>0.001936130378126653</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002467691282344107</v>
+        <v>0.005748142678064683</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001037886654897273</v>
+        <v>0.001324755168234438</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002113118500982986</v>
+        <v>0.002655160926891522</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001063704841337383</v>
+        <v>0.001312003587352169</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.000434516243214146</v>
+        <v>0.001106897366065493</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001221523623254156</v>
+        <v>0.00160638221323134</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003213448723222532</v>
+        <v>0.004741821027387311</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.002033547288354226</v>
+        <v>0.008772328370541194</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00485633504031503</v>
+        <v>0.008503609966880526</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007503726009311467</v>
+        <v>0.0002683290159144287</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0001447913468278788</v>
+        <v>0.0005340913266530904</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002494258061987034</v>
+        <v>0.003789951159164066</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00334794913871802</v>
+        <v>0.01078186540161102</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.001917819652293379</v>
+        <v>0.01116129897999361</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001285717804441414</v>
+        <v>0.001111007914515769</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005727390534803221</v>
+        <v>0.009068677495294617</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002382659856901792</v>
+        <v>0.001413466497075591</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002878921362212237</v>
+        <v>0.002026292229970932</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006521124417269249</v>
+        <v>0.0006729714446541065</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001038892552369148</v>
+        <v>0.002004466346228523</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003478627558477615</v>
+        <v>0.0115658101467795</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001537811063951904</v>
+        <v>0.00199088182572059</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001649394155067502</v>
+        <v>0.002777186302337504</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001688197702680999</v>
+        <v>0.002370958314565525</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002414182633988645</v>
+        <v>0.001413943203531642</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001927826360834632</v>
+        <v>0.0008817410181144206</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001314874510159065</v>
+        <v>0.003012739036289975</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002788154713915661</v>
+        <v>0.002354938381221796</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001769177730758417</v>
+        <v>7.017818630330684e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001966512067479675</v>
+        <v>0.004423829423997655</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003915404772587045</v>
+        <v>0.007170259260547565</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004923561855103745</v>
+        <v>0.006719047263829089</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001409645845282931</v>
+        <v>0.001449412103867721</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0005853547906642569</v>
+        <v>0.001611475054400876</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001248074915595668</v>
+        <v>0.002924118982514336</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002581009168214089</v>
+        <v>0.002719464282119874</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002199190351134033</v>
+        <v>0.004297566708334936</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001520503376454038</v>
+        <v>0.002058044343972745</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0008977725879177179</v>
+        <v>0.002650447452238213</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001209907519167466</v>
+        <v>0.005679568077524353</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0007393583920610963</v>
+        <v>0.001636816210822785</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001164054282944789</v>
+        <v>2.458844090723722e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001278707269741482</v>
+        <v>0.001197343741642057</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.004037875219694634</v>
+        <v>0.004995504212163462</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001477415396633572</v>
+        <v>0.001580221874921083</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0008073368122522752</v>
+        <v>0.0008124148427400757</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001109097898125878</v>
+        <v>0.00173185588034539</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0001268775806900966</v>
+        <v>0.0004484158945498741</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002595854144772391</v>
+        <v>0.003910460995951173</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.005437853020844695</v>
+        <v>0.007506181469141855</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.003011397740261088</v>
+        <v>0.002246957758780977</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001161713059165059</v>
+        <v>0.001350768515773944</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001241685540106793</v>
+        <v>0.0002581938269720542</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003921510185560316</v>
+        <v>0.000182541668907789</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001492619317769918</v>
+        <v>0.001803647844199122</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.004879327640051294</v>
+        <v>0.01041323749026859</v>
       </c>
       <c r="CZ4" t="n">
-        <v>8.049860359883093e-05</v>
+        <v>0.0001661386123072162</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0003566093166250049</v>
+        <v>0.0005003448368993117</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001736204417310948</v>
+        <v>0.001804433759997826</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003252581262366296</v>
+        <v>0.00329860554674235</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0005446936636186757</v>
+        <v>0.0003892656159936654</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0007889914895509718</v>
+        <v>0.001528324781255849</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.002283897710565551</v>
+        <v>0.003045785826284923</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001559697639312194</v>
+        <v>0.001309134056133122</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002321116731535257</v>
+        <v>0.003452408074829792</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001691144187864624</v>
+        <v>0.002326521111256775</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0005562550912961693</v>
+        <v>0.0003426414546253124</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0009552995279149595</v>
+        <v>0.0009701064196649896</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001826372167081696</v>
+        <v>0.0001283803773068223</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0006504962052030163</v>
+        <v>0.001604038210165442</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001788389710445019</v>
+        <v>0.001862259149431485</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003852878660733147</v>
+        <v>0.002565732866323004</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001715091023956672</v>
+        <v>0.003695558706978021</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004368002207143816</v>
+        <v>0.0004151434127660671</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.000256812254485144</v>
+        <v>0.0006060759320838308</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001395561462237433</v>
+        <v>0.000349266002606087</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001950063183225013</v>
+        <v>0.002177314486476883</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002014001614360328</v>
+        <v>0.002954541126645663</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002005096572864997</v>
+        <v>0.000260953870464062</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0006607165392565132</v>
+        <v>0.001341686007367098</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001657854861010801</v>
+        <v>0.002121647035948518</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0001809427434495442</v>
+        <v>0.0001406054018798751</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001718954084275598</v>
+        <v>0.001136729283552282</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003332677573511963</v>
+        <v>0.002550220627034172</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.002392732735204939</v>
+        <v>0.002135436856972097</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001193955966715184</v>
+        <v>0.001355123192299728</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001509965334034413</v>
+        <v>4.082114019150432e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0005172638375328418</v>
+        <v>0.0008503798942559642</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0004168245247249798</v>
+        <v>0.001188932098693614</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004909858633758975</v>
+        <v>0.000181794351375401</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0006605750929290862</v>
+        <v>0.001270515644645361</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.000971461675315397</v>
+        <v>0.0009119839790589666</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001958180784562216</v>
+        <v>0.001971200725317994</v>
       </c>
       <c r="EL4" t="n">
-        <v>2.692445857955065e-05</v>
+        <v>0.0002508573038864322</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002325321167762755</v>
+        <v>0.0004160160198696409</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0005428898545367688</v>
+        <v>0.0001001604856468782</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003854884041085311</v>
+        <v>0.0001623591704508884</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0007651988123711933</v>
+        <v>0.001338379935684479</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>0.0001180504959465563</v>
       </c>
       <c r="ES4" t="n">
-        <v>2.586438229989563e-05</v>
+        <v>0.0001238667126080802</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0007170979062407404</v>
+        <v>0.0006287958103600913</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.000426375515120551</v>
+        <v>0.0004101635892423372</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002818336234833727</v>
+        <v>0.0002224882864960142</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.000882028610511237</v>
+        <v>0.001153890397985947</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0008277361962148342</v>
+        <v>0.002549524072396408</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0003096573695507133</v>
+        <v>0.0004387894911654865</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007989690721649456</v>
+        <v>-0.007646048109965642</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.002736750651607289</v>
+        <v>-0.001288659793814428</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001293900184842822</v>
+        <v>-0.001633224451703219</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004213727193744543</v>
+        <v>-0.002020676691729351</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001539897340177321</v>
+        <v>-0.0003040834057341124</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002753872633390731</v>
+        <v>-0.004596219931271461</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.001911381407471757</v>
+        <v>-0.005498120300751896</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.003462230215827344</v>
+        <v>-0.008462199312714825</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.004946043165467628</v>
+        <v>-0.004682130584192423</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001721170395869187</v>
+        <v>-0.002333177788147456</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0003597122302157807</v>
+        <v>-0.0009799346710219314</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001303214596003488</v>
+        <v>-0.002878006872852223</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.003665413533834594</v>
+        <v>-0.004952215464813159</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.001478743068391808</v>
+        <v>-0.002104810996563566</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002519832011199252</v>
+        <v>-0.003442340791738352</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.00588487972508589</v>
+        <v>-0.01188909774436094</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001353243117125524</v>
+        <v>-0.002584586466165439</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.002113309352517956</v>
+        <v>-0.01447594501718219</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001493233784414372</v>
+        <v>-0.001476976542137221</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.004479701353243115</v>
+        <v>-0.002018900343642605</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0009398496240601517</v>
+        <v>-0.005627147766323004</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0005395683453237043</v>
+        <v>-0.007173539518900329</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004733218588640287</v>
+        <v>-0.005299739357080768</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0005163511187607605</v>
+        <v>-0.002882960413080871</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00229316546762588</v>
+        <v>-0.002067669172932374</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.003258036490008676</v>
+        <v>-0.01273496240601507</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0009466437177280574</v>
+        <v>-0.0007384882710686047</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003057553956834513</v>
+        <v>-0.003092783505154628</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.002061855670103085</v>
+        <v>-0.003336466165413543</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01622203098106714</v>
+        <v>-0.01721170395869189</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.005125977410946969</v>
+        <v>-0.005636833046471568</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0009466437177280574</v>
+        <v>-0.002362542955326452</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001663585951940794</v>
+        <v>-0.002053196453569761</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.0009442446043165132</v>
+        <v>-0.001030927835051543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.002832733812949606</v>
+        <v>-0.004862306368330438</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02185886402753873</v>
+        <v>-0.01269248716752216</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.000854316546762579</v>
+        <v>-0.0009122502172023816</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.004510309278350499</v>
+        <v>-0.01550687285223373</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005083179297596985</v>
+        <v>-0.006203007518797021</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005292598967297779</v>
+        <v>-0.00747422680412374</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0003597122302157807</v>
+        <v>-0.005926271581894538</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.001737619461337958</v>
+        <v>-0.00635738831615118</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01501721170395869</v>
+        <v>-0.01914802065404471</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.0005163511187607605</v>
+        <v>-0.002920962199312704</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004381443298969057</v>
+        <v>-0.01576460481099662</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001978417266187016</v>
+        <v>-0.00227663230240549</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.004479701353243115</v>
+        <v>-0.006066262249183385</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.001161790017211706</v>
+        <v>-0.003006872852233666</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0006024096385542355</v>
+        <v>-0.002613159122725151</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.001936316695352835</v>
+        <v>-0.002634011090573041</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.001753597122302131</v>
+        <v>-0.002426504899673354</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.002006532897806812</v>
+        <v>-0.01346655082536918</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.007186187587494164</v>
+        <v>-0.003593093793747082</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0009704251386321028</v>
+        <v>-0.0003147482014388192</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0001303214596003466</v>
+        <v>-0.001546391752577314</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.001694178974804506</v>
+        <v>-0.009659356042930467</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.007699486700886604</v>
+        <v>-0.008446103593093789</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.002147766323024047</v>
+        <v>-0.02701890034364263</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001247848537005147</v>
+        <v>-0.002799813345776947</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.01146907216494844</v>
+        <v>-0.00584192439862542</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.004083405734144197</v>
+        <v>-0.002065404475042998</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.005739617358842741</v>
+        <v>-0.003477443609022568</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0009466437177280462</v>
+        <v>-0.001798561151079137</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.00253872633390706</v>
+        <v>-0.001866542230517965</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.001911381407471757</v>
+        <v>-0.01615986099044304</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.00318853974121992</v>
+        <v>-0.003565292096219919</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.0007643884892085895</v>
+        <v>-0.005927835051546371</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.0009122502172024261</v>
+        <v>-0.006066262249183385</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.0006469500924213723</v>
+        <v>-0.001042571676802728</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0006294964028776606</v>
+        <v>-0.002193187120858608</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002846476901539896</v>
+        <v>-0.007092860475968266</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.008026131591227248</v>
+        <v>-0.007326178254783012</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.000419972001866542</v>
+        <v>-4.344048653344146e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.001893287435456103</v>
+        <v>-0.00949312714776639</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003092783505154628</v>
+        <v>-0.007606159589360706</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.008399440037330841</v>
+        <v>-0.00627147766323023</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.003147482014388481</v>
+        <v>-0.003406439570695286</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001216333622936572</v>
+        <v>-0.002893140457302845</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.0018041237113402</v>
+        <v>-0.005283505154639168</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.006112925804946334</v>
+        <v>-0.0027061855670103</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.005319645356976199</v>
+        <v>-0.003703703703703731</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003453103126458234</v>
+        <v>-0.003565292096219919</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.001172893136403108</v>
+        <v>-0.008075601374570474</v>
       </c>
       <c r="CH5" t="n">
+        <v>-0.007142857142857162</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.004467353951890018</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-4.257130693912093e-05</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.002939804013065794</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.005756013745704469</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.002960526315789502</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.001086012163336181</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.005516941789747998</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0.0008866075594960332</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.00868809730668979</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.01997422680412375</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.004512558535547084</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.001277139208173717</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0.0007643884892086117</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.0003266448903406438</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.005550774526678115</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.01211340206185574</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.0013339070567986</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.002823631624674128</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.005412371134020611</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.0008866075594960332</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.002345786272806205</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.007173539518900362</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.003040834057341413</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.005619412515964284</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.003546430237984133</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.0005132991133924402</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.0009450171821305808</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-0.0002333177788147456</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.001446570228651423</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.005278842060451283</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.007774914089347107</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.006768837803320582</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.0009991311902692757</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0.0002772643253235119</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.0006081668114682248</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>-0.003301476976542095</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.00498281786941579</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0.0006454388984509229</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>-0.003126458236117591</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0.004299702000851435</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0.0003266448903406438</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.00124768946395567</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.004526364909006065</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>-0.002852277564921279</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.0008992805755395517</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0.002256279267773531</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0.002969018932874323</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0.003049828178694147</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.001679888007466168</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.001617709663686717</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0.000793280447970135</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>-0.0002799813345776947</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0.0001866542230517965</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0.0001399906672888474</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0.001633224451703219</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0.0003733084461035929</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.0004621072088724975</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>-0.0006884681583476437</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>-0.0006081668114682248</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>-0.0007384882710685936</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0.001166588894073728</v>
+      </c>
+      <c r="EY5" t="n">
         <v>-0.0009879725085910618</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>-0.001376936316695365</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.001306579561362575</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>-0.01219931271477662</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>-0.004170286707211091</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>-0.001476976542137254</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-0.002823631624674161</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>-0.0001348920863309178</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>-0.007254561251085978</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>-0.01494845360824747</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>-0.005756013745704447</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>-0.002113309352517945</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>-0.0002151462994836595</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>-0.0003872633390705871</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.003147482014388492</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>-0.0122852233676976</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.0002172024326672628</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>-0.0004496402877697259</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>-0.00490877497827974</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-0.009296264118158093</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>-0.0004344048653345034</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-0.002128583840139009</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>-0.005440647482014382</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.001911381407471735</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>-0.002925989672977625</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.002753149790013998</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-0.0006081668114682693</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-0.001592082616178991</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>-4.30292598967319e-05</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>-0.001288659793814428</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>-0.004993000466635556</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>-0.01152589827344843</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>-0.0009036144578313254</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>-0.001259916005599626</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>-0.0007393715341958762</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>-0.004013065795613624</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>-0.003141135972461295</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>-0.004479701353243115</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>-0.0005163511187607717</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>-0.001618705035971191</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>-0.0007643884892086006</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>-0.0001348920863309178</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>-0.004479701353243115</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>-0.009239384041063925</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>-0.004479701353243115</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>-0.001202749140893467</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>-0.0004699248120301203</v>
-      </c>
-      <c r="EF5" t="n">
-        <v>-0.0006999533364442367</v>
-      </c>
-      <c r="EG5" t="n">
-        <v>-0.0004666355576294912</v>
-      </c>
-      <c r="EH5" t="n">
-        <v>-0.0004946043165467318</v>
-      </c>
-      <c r="EI5" t="n">
-        <v>-0.0004621072088724087</v>
-      </c>
-      <c r="EJ5" t="n">
-        <v>-0.0005545286506468794</v>
-      </c>
-      <c r="EK5" t="n">
-        <v>-0.000785582255083106</v>
-      </c>
-      <c r="EL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM5" t="n">
-        <v>-0.0005083179297596496</v>
-      </c>
-      <c r="EN5" t="n">
-        <v>-8.60585197934638e-05</v>
-      </c>
-      <c r="EO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP5" t="n">
-        <v>-0.0006454388984509674</v>
-      </c>
-      <c r="EQ5" t="n">
-        <v>-0.0001322751322751281</v>
-      </c>
-      <c r="ER5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES5" t="n">
-        <v>-4.699248120301203e-05</v>
-      </c>
-      <c r="ET5" t="n">
-        <v>-0.001663669064748174</v>
-      </c>
-      <c r="EU5" t="n">
-        <v>-0.0006007393715341314</v>
-      </c>
-      <c r="EV5" t="n">
-        <v>-0.0004733218588640509</v>
-      </c>
-      <c r="EW5" t="n">
-        <v>-0.0003006872852233666</v>
-      </c>
-      <c r="EX5" t="n">
-        <v>-0.0002172024326672628</v>
-      </c>
-      <c r="EY5" t="n">
-        <v>-0.0001399906672888474</v>
       </c>
     </row>
     <row r="6">
@@ -3083,430 +3083,430 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0006715891820798014</v>
+        <v>-0.0008763769374364738</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0007943298780568237</v>
+        <v>0.0002379311892445418</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0002799813345776947</v>
+        <v>-0.0004734644490153622</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0007103063117670726</v>
+        <v>-0.0002577319587628857</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0003026959875398583</v>
+        <v>-8.44474292372166e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0007550679748922068</v>
+        <v>-0.000512013190890151</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0008018008326079352</v>
+        <v>-0.0007910810526836093</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.002062299270720577</v>
+        <v>-0.0005317557414327128</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001191372633390697</v>
+        <v>-0.001462377407771193</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0009944870593076916</v>
+        <v>-4.380761468388561e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.258036490008942e-05</v>
+        <v>-0.0001778474127913987</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0006640363680593259</v>
+        <v>-0.0004317201221672951</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001682391033445696</v>
+        <v>-0.002096761899960653</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0001569379417100974</v>
+        <v>-0.0006915710661578645</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0001348920863309261</v>
+        <v>-0.001674105740184914</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.002421295073790408</v>
+        <v>-0.000916899757780848</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0007511719811577361</v>
+        <v>-0.0008583682961209399</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.000658761977490499</v>
+        <v>-0.0007040420295342603</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0004429632985340992</v>
+        <v>-0.0003461189007152587</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.00130539365500078</v>
+        <v>-0.0006023774074534028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0006707705285029287</v>
+        <v>6.87206884049496e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0001633224451703219</v>
+        <v>-0.0009687216169569024</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0006077816648307949</v>
+        <v>-0.003742130174834693</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0001756354842744639</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.00170275075575538</v>
+        <v>-0.0007025944834016529</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0001996509581975253</v>
+        <v>-0.005246386412350939</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.000367866060123867</v>
+        <v>-0.0001254887519446801</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0001762218045113034</v>
+        <v>-0.0004127650260743465</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0007020876793068925</v>
+        <v>0.0002306860124729554</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002723127551032484</v>
+        <v>-0.002070212505796207</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00118341913539948</v>
+        <v>-0.002648472490150133</v>
       </c>
       <c r="AG6" t="n">
-        <v>8.514261387824185e-05</v>
+        <v>-0.0007799150320434183</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006170302518494098</v>
+        <v>-0.000234918494396455</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.158501548613245e-05</v>
+        <v>-0.0005644007128223383</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0003861825700906208</v>
+        <v>-0.001963943614873498</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0009905992731588042</v>
+        <v>-0.001469806927111614</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.530120481927527e-05</v>
+        <v>-0.0002148258288008992</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001649886986962135</v>
+        <v>-0.001781578187166541</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001960921864012535</v>
+        <v>-0.0005864465682015318</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001586789717948312</v>
+        <v>-0.004096555394510343</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.298748536914204e-05</v>
+        <v>-0.001438189587819422</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0005249650023331747</v>
+        <v>-0.0009841287845136076</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0006163263210397979</v>
+        <v>-0.005390946023218388</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.000114997049685861</v>
+        <v>-0.001324131689376729</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.001025391410687537</v>
+        <v>-0.001530689780323718</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0002426062846580146</v>
+        <v>-0.0005198706099815513</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0003634665367121676</v>
+        <v>-0.001533836348355794</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0009498047851965645</v>
+        <v>-0.0009135475532444898</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>-0.0005033047997603346</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0009209128264350497</v>
+        <v>-0.000319383776476756</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.435065635183472e-05</v>
+        <v>-0.001346183339730272</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.000276617490223946</v>
+        <v>-0.004806346243583759</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.002426854111982985</v>
+        <v>-0.002434622915173346</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0.0001375733653667138</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.310536044362599e-05</v>
+        <v>-0.0005706744128506358</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0003754225026973562</v>
+        <v>-0.00235931323153244</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001522283106785674</v>
+        <v>-0.006319962393471442</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0003111212338930469</v>
+        <v>0.0001997180451127706</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.499766682221184e-05</v>
+        <v>-3.372302158272111e-05</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.002216043581175175</v>
+        <v>-0.002473131737260681</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005291996561480744</v>
+        <v>-0.0005574133786764246</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001028648730500101</v>
+        <v>-0.001303145627827607</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>-0.0003265316816217195</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.00128939374273774</v>
+        <v>-0.0006150046658300074</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001268495512868045</v>
+        <v>-0.004572991746593391</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0002821086504290387</v>
+        <v>-0.0005910171949321142</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.000245357456096959</v>
+        <v>-0.001879112664418869</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.000121232618036396</v>
+        <v>-0.00100867581796634</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0001613597246127446</v>
+        <v>2.15146299483715e-05</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0001918588958670642</v>
+        <v>-6.516072980014553e-05</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.000162647376592348</v>
+        <v>-0.0015415397567004</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001860318973736652</v>
+        <v>-0.001029858530425709</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001305499909368765</v>
+        <v>-0.0002988113206292775</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0001501959352058491</v>
+        <v>-0.003865685270104804</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001479072765883671</v>
+        <v>-0.004392346607258906</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.00070068815568681</v>
+        <v>-0.0003543814432989678</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003595011674286969</v>
+        <v>-0.0009469578224224423</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0005572649160364957</v>
+        <v>-0.002053196453569761</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0005652674822620191</v>
+        <v>-0.001104230612833157</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0008476195085177412</v>
+        <v>-0.001806844501707369</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0008686948087469476</v>
+        <v>-0.002437957944419639</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.00010116906474818</v>
+        <v>-0.0009608546177242771</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0001311348294106868</v>
+        <v>-0.001489491396573453</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0004717405520225703</v>
+        <v>-0.0009640681082455805</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-7.075833498650097e-05</v>
+        <v>-2.041647387523438e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.000864875194920095</v>
+        <v>-0.002264551464869091</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.000642608026089339</v>
+        <v>-5.489655894330148e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0001624920735573937</v>
+        <v>-9.664948453608213e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0002814614990579778</v>
+        <v>-0.0007833980705275495</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.001040121006321362</v>
+        <v>-0.0002692295665226246</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.0002285509724693019</v>
+        <v>-0.002411159674209257</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.0004967712576926409</v>
+        <v>-0.00179191662136613</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0001403124016393975</v>
+        <v>-0.0003250759088913868</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-9.774109470024329e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0001288659793814428</v>
+        <v>-0.000133097544952529</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0005435420140197321</v>
+        <v>-0.001125051050157857</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0005389141068097653</v>
+        <v>-0.002418326577738836</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-3.306878306878202e-05</v>
+        <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>-0.0003733084461035929</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.001433530974478281</v>
+        <v>-0.0009387986309639801</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.000299310180702625</v>
+        <v>-0.003093367636708453</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0002373357963186051</v>
+        <v>-6.516072980016218e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0003428745726411275</v>
+        <v>-0.0008939974457216226</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0007514902580123329</v>
+        <v>-0.003428610840945357</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.001096298090615264</v>
+        <v>-0.0004468028850734718</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001628927911275369</v>
+        <v>-0.002972252389409044</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0002968222094728135</v>
+        <v>-0.001521707891418808</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0002185580490178113</v>
+        <v>-0.0002605616551232565</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.001066002074681802</v>
+        <v>-0.0003806676880717397</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
+        <v>-0.000464812281248736</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.002155372809306672</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.002144459131489954</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.002533073960722332</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.0001283247783481101</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.0002578320946621748</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0.002419569854248141</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0.001477669100725687</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0.0002304798562226984</v>
+      </c>
+      <c r="DX6" t="n">
         <v>-6.744604316545887e-05</v>
       </c>
-      <c r="DN6" t="n">
-        <v>-0.0004243074754788801</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-0.001989685703468735</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>-0.0006008945460450332</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>-0.0001277139208173628</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>-3.499766682221183e-05</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>-0.001637168009259316</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>-0.00101473332612104</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>-0.001669610843691574</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>-0.0005488379812479849</v>
-      </c>
       <c r="DY6" t="n">
-        <v>-0.0001107021196733421</v>
+        <v>-0.0005404825862046298</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.166588894073728e-05</v>
+        <v>-6.454388984508951e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.000207915222283031</v>
+        <v>-0.0003865979381443258</v>
       </c>
       <c r="EB6" t="n">
-        <v>2.248201438850017e-05</v>
+        <v>-2.400555663198134e-05</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.001453566528220709</v>
+        <v>-0.0004926809703914514</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0006869277860125755</v>
+        <v>-0.000103974121996317</v>
       </c>
       <c r="EE6" t="n">
-        <v>-3.499766682221183e-05</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0002744368079419552</v>
+        <v>-0.00111245164548279</v>
       </c>
       <c r="EG6" t="n">
-        <v>-4.448033655690963e-05</v>
+        <v>-0.0009412933143003177</v>
       </c>
       <c r="EH6" t="n">
-        <v>-3.221649484536071e-05</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0.0006841876629018028</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-6.613756613756404e-05</v>
+        <v>-0.0006666184784323486</v>
       </c>
       <c r="EK6" t="n">
-        <v>-6.744604316545887e-05</v>
+        <v>-0.0004941075443137654</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0.0001082021647578951</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0.0005856308855225506</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0003364936313482725</v>
+        <v>-0.000177847412791407</v>
       </c>
       <c r="EU6" t="n">
-        <v>-7.509796760292453e-05</v>
+        <v>-0.0002561760995217571</v>
       </c>
       <c r="EV6" t="n">
-        <v>-3.221649484536071e-05</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0001739247521900328</v>
+        <v>-0.0002674656821439692</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.174812030075023e-05</v>
+        <v>-0.0004237409004815479</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>1.155268022181022e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3552,454 +3552,454 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0.0001142801101078561</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0005850072749730706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0008150688006824724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.420225765525698e-05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0001382911403028819</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.699248120297872e-05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.666355576293801e-05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8.64463832697504e-05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.0002516655806593215</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.310536044362044e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-6.45438898450923e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002894514439227169</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.0009248496166574637</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.0001763668430335041</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.000256504245827166</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.001677527709633053</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0001300023636793546</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0005859063006321385</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0001506024096385394</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0002027638540796406</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0006091582672559214</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0001160776324373114</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.001284150785366506</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.0005756726924815769</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-8.497634929827149e-07</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.001541659464753792</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.003905044524546564</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.001806749872766161</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.0007608992171342145</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-4.257130693912648e-05</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2.147766323024047e-05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0009597276848209823</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.0003458918688803714</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.007650268673949722</v>
+      </c>
+      <c r="AL7" t="n">
         <v>2.333177788147456e-05</v>
       </c>
-      <c r="C7" t="n">
-        <v>-0.0001292343246366179</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-2.151462994836595e-05</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-7.445194311079815e-05</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.0001115151993982266</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.000363077824044028</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.0002161243741690133</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.0006835843411489239</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.0005168656344107958</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0001282899500994028</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0001322751322751281</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.0004356559083111278</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.0005282447750100394</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0006567434978018926</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.172024326674849e-05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6.03464596743708e-05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.0001702852277564615</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.001202610830257678</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.0002469803490077249</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.000585418501609769</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.0002497955424938803</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.0003976994182446181</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.0002413203536787256</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-4.666355576294911e-05</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.0002559786718539347</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0003477486210265668</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AM7" t="n">
+        <v>0.001140685271187703</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0002808373192065006</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.001962810724487296</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8.963380673907007e-05</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.0002697841726618578</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.002392265385686393</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.712391645234184e-05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.090712392492148e-05</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.0002697507125181242</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.0002544017417644651</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.0001134077920892651</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.0001879699248120481</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.0003108227703551902</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.00015513794752266</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.001637349124531795</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.000584532374100727</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-8.961888222343006e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.0003588046345708196</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.0009997270382927248</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.002520404311471425</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.0009072889386145588</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.0001107546107323387</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.001248081490443886</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.0001393114149753072</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.0002148738298770992</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-4.902093362903482e-05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0.0006322604808802368</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0.0003015423262407668</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.0003017980923688712</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.0003670598629501532</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.0003472596589678911</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.744604316548108e-05</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-0.0001543209876543161</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.0002010914373861305</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.0001826419328076922</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0007005773487597344</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.001694260550495685</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.0008502263020335854</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>4.666355576294911e-05</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>-0.0002227429013748283</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>2.505976123299281e-05</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.0005907164819264676</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0.001125960134148313</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0.0005582423706139928</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.0005148018840805512</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0.0002968669740001539</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.000512288581832987</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0.0003474860764057619</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.0001977092544617865</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>6.56766673827358e-05</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0.0004443861818146821</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.0001089268284461098</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.0005464976677661715</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.001223544973544966</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-9.359408224815513e-05</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>6.831836118409429e-05</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>-0.0007143861999121704</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0.0001786094229976442</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.0003481881488754613</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0.0004989677389327152</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2.204585537919357e-05</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.0004436924103233709</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.000484661739096931</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0.0001299945265462288</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-4.621072088725753e-05</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.0001774263480979532</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-4.496402877697258e-05</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>-3.699434807443171e-05</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0.0002544017417644873</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0.0002061282334264114</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.0008192849869752328</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0.0002483163844863801</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>2.128565346956046e-05</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>-0.0001652959978106772</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.0001776753200614545</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-4.395967761872677e-05</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.0008011811558242155</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.0002451951238248762</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.0003464835724286131</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0.0002324680153217518</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0001947544492910736</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0.0006693341787639639</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.0002730263050657544</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>9.108419196138807e-05</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.0001322751322751281</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-2.172024326672073e-05</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0.0004342578568723998</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
         <v>2.333177788147456e-05</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0.001207365596452559</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.001886401518076258</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.006384404212094086</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0005166003018236609</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0006846575935705202</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.0003479526571895985</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0006242821576158075</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.003236632735366318</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.002379871141838741</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.001020258538525065</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.004260527368350869</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.0007102739335449915</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-0.000306437904139728</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.0004262427977159089</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.0004482204379222754</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.003563653440558212</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.0001303214596003743</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.0003773964955020193</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.0003856378893409285</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.0001125666405835446</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.0003705465839841604</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.693672713495302e-05</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.0003246062154108054</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.0009026519575787428</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.0004162663553048729</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.000164473684210531</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.0001504545427660598</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.0001512801800158059</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.000472316581304616</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.0001984126984127033</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.351714031075595e-05</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.0003165153870775927</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.001268975117425242</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0004502043935640465</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-0.0003419443143857947</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.0001083586362971456</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-0.0007282017724999591</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-0.0005640698169433688</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.0002219789576111353</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0003153641480374003</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.0003671775223499374</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.0001826419328076756</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>-2.770234353766118e-06</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.000138291140302893</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-0.0006007393715341703</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>-6.461716231830894e-05</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.002269522423814663</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-2.736726874658644e-05</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>-0.0001512801800158059</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>-6.744604316545333e-05</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>-1.05950506442132e-06</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>2.280605728881556e-05</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-4.012710657634868e-05</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>-0.0003180159252885061</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.0001112887819604003</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.0003262112073158962</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>-6.831836118405545e-05</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.0004796874049747435</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>-6.058066853882884e-05</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>-0.0001774633932700498</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>4.409171075837603e-05</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>-4.496402877696703e-05</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>-7.048872180453469e-05</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0.0004610824635022936</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>-0.0001331730417395261</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0.0007511530113944509</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>4.257130693912093e-05</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>6.931608133088907e-05</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>-0.0006531308942459235</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-4.376766785803566e-05</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>-4.48519126680036e-05</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>-0.0002809681108978835</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>4.579529576054177e-07</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>-0.0001146127649954587</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>0.0001718056315757444</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>2.333177788147456e-05</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0.0001824054055868829</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>1.976524965030535e-05</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0.0001386321626617559</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>-4.496402877697258e-05</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-0.0001315149303655006</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>-8.963380673908118e-05</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>2.128565346956046e-05</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>-0.0003865979381443285</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>8.590281578786939e-05</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>-0.0002006465907035682</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>-0.0003572197125058629</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>0.0007787764815877173</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>8.63958129939335e-05</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>-2.056133183492279e-07</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>0.0001499154802021452</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>2.204585537918802e-05</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>-0.0001064282673478023</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>0.0001975526858207011</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>0.0001174812030075079</v>
-      </c>
-      <c r="EH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI7" t="n">
-        <v>0.0001607506001657488</v>
-      </c>
-      <c r="EJ7" t="n">
-        <v>0.0001344283233351451</v>
-      </c>
-      <c r="EK7" t="n">
-        <v>4.699248120300092e-05</v>
-      </c>
-      <c r="EL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ7" t="n">
-        <v>0.0001750191929073053</v>
-      </c>
-      <c r="ER7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES7" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET7" t="n">
-        <v>0</v>
-      </c>
       <c r="EU7" t="n">
-        <v>0.0002051513970890262</v>
+        <v>4.420225765524587e-05</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4008,10 +4008,10 @@
         <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001493835938082833</v>
+        <v>-0.0002401239927597998</v>
       </c>
       <c r="EY7" t="n">
-        <v>0</v>
+        <v>0.0001641447587704459</v>
       </c>
     </row>
     <row r="8">
@@ -4021,376 +4021,376 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001584512653789755</v>
+        <v>0.0004439616306281258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006192191711846928</v>
+        <v>0.0009228851182874116</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005291005291005123</v>
+        <v>0.001320332622790676</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001396510411320773</v>
+        <v>0.0004692002822455605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001705606428661049</v>
+        <v>0.0003589255479086312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009762610286411261</v>
+        <v>0.002079915241644903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0005627662241979303</v>
+        <v>0.001683467128869442</v>
       </c>
       <c r="I8" t="n">
-        <v>6.420868238413424e-05</v>
+        <v>0.000290802237074167</v>
       </c>
       <c r="J8" t="n">
-        <v>-9.139822777246842e-05</v>
+        <v>0.0004129246727931551</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005302012787624822</v>
+        <v>0.0002918985809631347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006405697451495219</v>
+        <v>7.048872180450138e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0001560538534378847</v>
+        <v>0.000832228468719387</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002006641862878097</v>
+        <v>0.0007976349843820314</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001161290966517017</v>
+        <v>0.000536206009527429</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000266479148303686</v>
+        <v>-3.372302158272944e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002193118395860408</v>
+        <v>0.003896406906206251</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0006280291190463832</v>
+        <v>0.0005851427988100954</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00282407088949069</v>
+        <v>0.002916821907789416</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.750177275950344e-05</v>
+        <v>7.629201014584808e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.806604634190474e-05</v>
+        <v>3.465804066541401e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001170724655808786</v>
+        <v>0.001140520819810176</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001106339940025194</v>
+        <v>0.001669973544973524</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005948029796713661</v>
+        <v>0.00196868170419334</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001484013938274603</v>
+        <v>0.0005215196496395514</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001589137884634825</v>
+        <v>0.002982396555089101</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002164610824249366</v>
+        <v>5.901009321931383e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.761522936780451e-05</v>
+        <v>0.0001314228440517401</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002870906741784374</v>
+        <v>0.002514363942490763</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.005165331690285537</v>
+        <v>0.005216501402052967</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.008314954928930633</v>
+        <v>0.007700592594238581</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003919738684087726</v>
+        <v>0.002103915694648029</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001398627087913629</v>
+        <v>0.0004738230845963753</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001399906672888473</v>
+        <v>0.0001068083683026216</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001822654251608394</v>
+        <v>0.00134792915324021</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004418723672149194</v>
+        <v>0.002309460153973697</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.009900386363320532</v>
+        <v>0.01529195881704004</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001553174172544755</v>
+        <v>0.0008901014109347182</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.005826001695456065</v>
+        <v>0.005004204755654179</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0001227726084047809</v>
+        <v>0.0008818971421090033</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0009856017758316988</v>
+        <v>0.0006828917642226623</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0009205510797272192</v>
+        <v>0.0008532137285008708</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00146460623601517</v>
+        <v>0.0007306481565359319</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.007452533919507701</v>
+        <v>0.005499046977115116</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006344624562988538</v>
+        <v>0.0007803309847819045</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001440914555334733</v>
+        <v>0.001206796643487989</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.000957334011614605</v>
+        <v>0.0006349331034312122</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0008377952162109431</v>
+        <v>0.001031489305518932</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0002151606518237648</v>
+        <v>0.00023620297647442</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.000528191421662208</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0003743763289925234</v>
+        <v>0.001085498007065819</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002650275459553791</v>
+        <v>0.0007575362016151832</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001924541888454953</v>
+        <v>-4.992408238712888e-05</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0033346728347452</v>
+        <v>0.001636670448284741</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0005430242272347286</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002043150510732256</v>
+        <v>-2.349624060150601e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001373744677033861</v>
+        <v>0.001334329706397516</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002402421537054339</v>
+        <v>0.001040091248235511</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001089886476599181</v>
+        <v>0.002186304863626398</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001130397891169388</v>
+        <v>0.0003612909588786656</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0034386453831771</v>
+        <v>0.002061143825551631</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001246476179938516</v>
+        <v>0.001252697716513551</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0007605820105819867</v>
+        <v>0.0007576719236171758</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0005442212663333446</v>
+        <v>0.0002931732262026115</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.0001858617620193071</v>
+        <v>0.001438844636697972</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0006776905662429445</v>
+        <v>0.000842160387595603</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001091341717569702</v>
+        <v>0.00150470102049958</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001254656802027557</v>
+        <v>0.001001599037643455</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001581704842121315</v>
+        <v>0.0007655535343459141</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0006904940905174045</v>
+        <v>0.001525991480293065</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0009207045391255581</v>
+        <v>0.0003022672701387785</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0007729160814721303</v>
+        <v>0.000699431086640237</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0005220336521379986</v>
+        <v>0.0002120074711069009</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001762218045112785</v>
+        <v>0.001101186875607488</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002419522440317262</v>
+        <v>0.001982060094756544</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.004576457263715097</v>
+        <v>0.002638068545312458</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001078935746388815</v>
+        <v>0.001066755381985432</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003773513864507694</v>
+        <v>0.0008877860117920466</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001050916780986524</v>
+        <v>-1.102292768959401e-05</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001082824568139135</v>
+        <v>0.0009213647144682064</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003037242692592341</v>
+        <v>0.00032222835410044</v>
       </c>
       <c r="CF8" t="n">
-        <v>-8.594761963908736e-05</v>
+        <v>-6.93160813308502e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008054397250709554</v>
+        <v>0.0003827013577108462</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001301217914751246</v>
+        <v>0.0006399727672476791</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0006805686638434506</v>
+        <v>0.0003011887037267097</v>
       </c>
       <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.0007249922486628646</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.0001203798865669903</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.0006523841109298766</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.0001274750148551273</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-2.204585537918524e-05</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.0004521209596154874</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.002420498554519174</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.0001589324658572616</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.0005092354687678907</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.0007804715101005583</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>6.516072980017885e-05</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-0.0001824054055868579</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.0007732560627645574</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>9.920634920637107e-05</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.0008006048950119054</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.000528665413533802</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0.0001523622199829433</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.001170452468117244</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.000156937941710153</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>8.326672684688675e-18</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.001083144029709393</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.0007845927536042657</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.0002468011173870855</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0.0002300083793821683</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>3.19284802043407e-05</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.0002929331460207185</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>6.454388984511172e-05</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.0001069057231803838</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.0004852125693160791</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>7.556681753469463e-05</v>
+      </c>
+      <c r="DR8" t="n">
         <v>3.221649484536071e-05</v>
       </c>
-      <c r="CK8" t="n">
-        <v>0.001748700398753178</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.0001642036124794688</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0.000671527166211136</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0.0006789879375726588</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.0004215956049665404</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>3.499766682221183e-05</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.000209986000933271</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.002100440314201085</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0.0007842789904541292</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0.001348409102043793</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>3.465804066543899e-05</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>0.001027618595794433</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0.003257060195669897</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0.0001049930004666355</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>-4.62107208872381e-05</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.000592234614077941</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>0.0001718397892009865</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>-2.284269352542112e-05</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>0.0001644916271204888</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>0.0001732902033271949</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.00151017952679264</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.0006487365893629859</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>0.0006455804420690409</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>0.0004637088213583246</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>3.221649484536071e-05</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>0.0003499766682221184</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.0006922378014305175</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.0002606429192007043</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0.0003258524293081738</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>3.227194492254893e-05</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>8.134884343786452e-05</v>
-      </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>6.443298969072142e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0007203507483407561</v>
+        <v>0.0008446292873280498</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0005019512157233563</v>
+        <v>0.0004789592974503376</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4399,88 +4399,88 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-5.704352220139985e-05</v>
+        <v>0.0002156775249144954</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.00246389824011731</v>
+        <v>0.001290557256543384</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002419144811376117</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.000739884884867309</v>
+        <v>0.0004127200961001776</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001214976719959887</v>
+        <v>0.001319643383423547</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0009485452200667128</v>
+        <v>0.0002577319587628912</v>
       </c>
       <c r="ED8" t="n">
-        <v>9.247734803291552e-05</v>
+        <v>0.0008596106364300998</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0003632186177452118</v>
+        <v>5.447167719684343e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0005343412352078081</v>
+        <v>-2.248201438848629e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0003591153810451636</v>
+        <v>0.0001192557246486342</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0005088429837480034</v>
+        <v>0.0003585859217518417</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002307265503027789</v>
+        <v>0.000692551776803435</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.000164547077197677</v>
+        <v>0.0003151730831853522</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001209265924730724</v>
+        <v>0.0002579515335100036</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0003121978294230554</v>
+        <v>8.761522936782118e-05</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>3.258036490008942e-05</v>
+        <v>0.0001512101614188632</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0005957299195978067</v>
+        <v>0.0004250099982072708</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>6.454388984509786e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0003122619921457237</v>
+        <v>0.0001508080229569331</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0003399688008681401</v>
+        <v>0.0001867364544118094</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>6.999533364442366e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0004222610058927906</v>
+        <v>0.0001653439153439518</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0005812934276789611</v>
+        <v>-2.147766323024047e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>4.598319251735428e-05</v>
+        <v>0.0003844455318435857</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002911275415896542</v>
+        <v>0.006798623063683329</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00107326178254783</v>
+        <v>0.001353243117125524</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001781059947871433</v>
+        <v>0.002954144620811327</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00242504409171076</v>
+        <v>0.002239850676621558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009036144578313144</v>
+        <v>0.001543209876543272</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002020676691729295</v>
+        <v>0.003639757349510031</v>
       </c>
       <c r="H9" t="n">
+        <v>0.008993115318416556</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002108433734939774</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002333177788147456</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0008514261387824185</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001386321626617337</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.002624784853700546</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00424638357442837</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006712564543889898</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.002171136653895256</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.007428323197219855</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.003485370051635128</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.008605851979345991</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.001362281822051925</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.002426564495530004</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.005179654689687352</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.005550774526678182</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.00424638357442837</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.001166588894073728</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.003733084461035929</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01940619621342515</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0004666355576294912</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.006583476764199681</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.01129258049463369</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.01371908539430704</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.005226318245450301</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.002402957486136781</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.004432013769363208</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.004390018484288327</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.006813909774436066</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0317549956559514</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.003055077452667843</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.01125108601216337</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.004819277108433784</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.001149425287356309</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.001617709663686662</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.004039965247610811</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.005972935137657487</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.003126458236117591</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.004044750430292621</v>
+      </c>
+      <c r="AU9" t="n">
         <v>0.002006532897806812</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.001691729323308266</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0006532897806812877</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001155268022181188</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0009879725085910618</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.001932989690721643</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.003219785347643489</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.002736750651607312</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.0008928571428571286</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.009730668983492641</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.002085143353605567</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.005263157894736836</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.000430292598967319</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.001493233784414372</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.002939804013065794</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.001550751879699253</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.006626224918338775</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.0002577319587628857</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.002649869678540417</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.00300751879699247</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.0004699248120300092</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.01097246127366608</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.0103593093793747</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.01600559962669155</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.006578947368420995</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.002878006872852223</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.001456766917293217</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.005132991133924403</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.01550751879699246</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.03584656084656081</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.002053196453569761</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.01275415896487991</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.001633224451703219</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.001632302405498276</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.001366843033509657</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.006056701030927814</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.01647223518432104</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.002631578947368407</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.004059729351376573</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.001539897340177321</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0.003996524761077325</v>
+        <v>0.003829604130808995</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002402957486136848</v>
+        <v>0.0005845323741007436</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000793280447970135</v>
+        <v>0.0006950477845352298</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002147766323024047</v>
+        <v>0.002341421881651751</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.009727443609022534</v>
+        <v>0.01407056798623066</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.00430292598967299</v>
+        <v>0.019750430292599</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.009509466437177283</v>
+        <v>0.02517211703958696</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001633224451703219</v>
+        <v>0.0006454388984509674</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0003289473684210176</v>
+        <v>0.0003733084461035929</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.007095864661654095</v>
+        <v>0.002818853974121993</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.003442340791738374</v>
+        <v>0.02852839931153188</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00488721804511274</v>
+        <v>0.01919104991394149</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003006872852233666</v>
+        <v>0.0007384882710686602</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.009470026064291958</v>
+        <v>0.02598967297762481</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.005039664022398504</v>
+        <v>0.002190721649484528</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004561251086012174</v>
+        <v>0.004087779690189352</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001353243117125524</v>
+        <v>0.0005212858384014196</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001042571676802795</v>
+        <v>0.005034423407917399</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.009982788296041312</v>
+        <v>0.02564543889845097</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001539897340177321</v>
+        <v>0.00271084337349401</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003873075128324777</v>
+        <v>0.002366609294320143</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.005039664022398504</v>
+        <v>0.001306579561362575</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.007606159589360706</v>
+        <v>0.00383141762452105</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005879608026131589</v>
+        <v>0.0005132991133924402</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00227663230240549</v>
+        <v>0.002333177788147456</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001866542230517965</v>
+        <v>0.00073149741824442</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.591065292096189e-05</v>
+        <v>0.0002128565346956046</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.004853009799346708</v>
+        <v>0.007444061962134274</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.008679421371908535</v>
+        <v>0.0183304647160069</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.008306112925804942</v>
+        <v>0.01660929432013773</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.00152495378927916</v>
+        <v>0.001303214596003521</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0005584192439862523</v>
+        <v>0.002667814113597278</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002333177788147456</v>
+        <v>0.005938037865748746</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.003712406015037572</v>
+        <v>0.006970740103270245</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.003436426116838476</v>
+        <v>0.01148881239242689</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002725563909774409</v>
+        <v>0.003012048192771111</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001679888007466168</v>
+        <v>0.001278659611993016</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003012048192771066</v>
+        <v>0.01471600688468161</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.000868809730669029</v>
+        <v>0.0008928571428570952</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0003733084461035929</v>
+        <v>4.409171075838714e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002577319587628857</v>
+        <v>0.001333907056798633</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002753149790013998</v>
+        <v>0.01282271944922551</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0008591065292096189</v>
+        <v>0.002366609294320155</v>
       </c>
       <c r="CN9" t="n">
+        <v>0.002065404475043075</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0005599626691553894</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0007237122179650557</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.005378657487091254</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.00737284181054596</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.003829604130809005</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.003126458236117591</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>8.818342151677428e-05</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0003436426116838476</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.0003289473684210065</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.02852839931153187</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0005154639175257714</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0001798561151079458</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.003442340791738419</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.00606712564543892</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0006007393715341758</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.002893140457302845</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.001033834586466109</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.001446570228651423</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.005593803786574902</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.004561101549053393</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.0005639097744360333</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.002469135802469102</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.000304083405734179</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.004475043029259928</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0002799813345776947</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0006999533364442367</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.005895008605852015</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0004046762589928532</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.001721170395869198</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0005639097744360444</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.003571428571428603</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.006282271944922568</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>9.242144177448174e-05</v>
+      </c>
+      <c r="DX9" t="n">
         <v>0.001213252449836677</v>
       </c>
-      <c r="CO9" t="n">
-        <v>0.001161790017211706</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0.0003012048192771011</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.002405498281786933</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.004339710685954267</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.003853383458646597</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.001987060998151624</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.0003006872852233666</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.001080827067669166</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.00180722891566264</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.004433037797480166</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>4.666355576294911e-05</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0.0008688097306690179</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.001506024096385539</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.002566495566962201</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.001293900184842933</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.001062846580406695</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.00214652356509566</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>0.002835051546391743</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.004293047130191319</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.004041353383458646</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>0.001030927835051543</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>0.001202749140893467</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.0005639097744360555</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>0.0008928571428571286</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.001268796992481191</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.002255639097744344</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.004170286707211146</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0.0003234750462107638</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0.0001399906672888474</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.0005639097744360555</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.003826411572561827</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.003033131124591693</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.0002799813345776947</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.0007988721804510935</v>
-      </c>
       <c r="DY9" t="n">
-        <v>0.004257167680278029</v>
+        <v>0.003126458236117591</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004733218588640397</v>
+        <v>0.0001763668430335486</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001201478743068418</v>
+        <v>0.002796901893287462</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002706486234251049</v>
+        <v>0.004647160068846856</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.004464285714285687</v>
+        <v>0.005593803786574892</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.002986467568828743</v>
+        <v>0.003593093793747082</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>0.0001290877796901957</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001080827067669143</v>
+        <v>0.0002349624060150046</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.000793280447970135</v>
+        <v>0.001787994891443134</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001293900184842922</v>
+        <v>0.0005599626691553894</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001781059947871433</v>
+        <v>0.00120481927710846</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.002893140457302845</v>
+        <v>0.001247848537005192</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.006019598693420436</v>
+        <v>0.005679862306368366</v>
       </c>
       <c r="EL9" t="n">
-        <v>8.514261387824185e-05</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003733084461035929</v>
+        <v>0.0009365687526606603</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.001691729323308255</v>
+        <v>0.0001866542230517965</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0009332711152589823</v>
+        <v>0.0003865979381443285</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.002473168455436303</v>
+        <v>0.003313253012048234</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>4.344048653345256e-05</v>
+        <v>0.0003759398496240074</v>
       </c>
       <c r="ET9" t="n">
+        <v>0.001773215118992066</v>
+      </c>
+      <c r="EU9" t="n">
         <v>0.0007302405498281761</v>
       </c>
-      <c r="EU9" t="n">
-        <v>0.0009466437177280684</v>
-      </c>
       <c r="EV9" t="n">
-        <v>0.0006109022556390453</v>
+        <v>0.0001721170395869276</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002566495566962201</v>
+        <v>0.003313112459169387</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.002473168455436303</v>
+        <v>0.007659208261617922</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0009036144578313254</v>
+        <v>0.0006066262249183385</v>
       </c>
     </row>
   </sheetData>
